--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -627,22 +627,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>5.5 m</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>5.67 m</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Τυπικό ύψος για Venlo-type θερμοκήπιο, εκτίμηση χωρίς πηγή</t>
+          <t>Μέσο ύψος τόξου, παράγεται από πραγματική γεωμετρία (πλευρικό 4.0m, κορυφή 6.5m, κόλπος 9.6m)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Δεν τεκμηριώθηκε — αντικατάσταση με πραγματικό σχέδιο</t>
+          <t>papers/geothermiki-s192g-quote.md — πραγματική προσφορά Γεωθερμική α.ε</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6.0 W/m²K</t>
+          <t>4.4 W/m²K</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Συντελεστής θερμικής απώλειας μονού γυαλιού θερμοκηπίου (όχι κτιρίου)</t>
+          <t>Διπλό φουσκωτό PE (όχι μονό γυαλί) — U-value με αέρα ανάμεσα στα δύο στρώματα</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>papers/greenhousemag-heat-loss.md — Greenhouse Management</t>
+          <t>papers/tunnelvisionhoops-double-layer.md (με επιφύλαξη πάχους φιλμ) · papers/geothermiki-s192g-quote.md</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -701,22 +701,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ποσοστό ηλιακής ακτινοβολίας που περνάει στο εσωτερικό</t>
+          <t>180μm θερμικό/anti-drip φιλμ, πραγματικό υλικό κάλυψης της προσφοράς — 88-92% PAR</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Βιβλιογραφικό εύρος 70-90% (γενικό, όχι συγκεκριμένη πηγή)</t>
+          <t>papers/greenhouse-film-180micron-transmission.md · papers/geothermiki-s192g-quote.md</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -738,22 +738,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Στέγη+τοίχοι ως πολλαπλάσιο της επιφάνειας δαπέδου</t>
+          <t>Υπολογισμένο από πραγματική γεωμετρία τόξου (5 κόλποι x 9.6m, rise 2.5m, μήκος 100m)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Γεωμετρική εκτίμηση, εξαρτάται από πραγματικό σχήμα κτιρίου</t>
+          <t>papers/geothermiki-s192g-quote.md — πλήρης παραγωγή στο αρχείο</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2193,7 +2193,6 @@
           <t>Οδηγός κατηγοριών</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Οδηγός" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1246,54 +1246,54 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Ποικιλία</t>
+          <t>Εξοικονόμηση θερμοκουρτίνας</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>crop.variety</t>
+          <t>climate_control.screen_energy_saving_fraction</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Beefsteak tomato</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>SITE-SPECIFIC</t>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Placeholder ποικιλία τομάτας</t>
+          <t>Ποσοστό μείωσης θερμικής απώλειας όταν η κουρτίνα είναι κλειστή (τη νύχτα)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Δεδομένο του χρήστη</t>
+          <t>papers/geothermiki-s192g-quote.md — πραγματικός εξοπλισμός τύπου PH55</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>config/greenhouse_example.yaml</t>
+          <t>config/greenhouse_example.yaml, twin/climate_model.py</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Ημερομηνία φύτευσης</t>
+          <t>Ποικιλία</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>crop.planting_date</t>
+          <t>crop.variety</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>Beefsteak tomato</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Placeholder ημερομηνία φύτευσης</t>
+          <t>Placeholder ποικιλία τομάτας</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1320,32 +1320,32 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Πυκνότητα φυτών</t>
+          <t>Ημερομηνία φύτευσης</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>crop.density_plants_per_m2</t>
+          <t>crop.planting_date</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2.5 φ/m²</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>SITE-SPECIFIC</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Φυτά ανά m² — τυπική εμπορική πυκνότητα single-stem high-wire καλλιέργειας</t>
+          <t>Placeholder ημερομηνία φύτευσης</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>papers/vt-extension-spes-474.md · papers/peet-welles-greenhouse-tomato-production.md</t>
+          <t>Δεδομένο του χρήστη</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1357,12 +1357,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Πυκνότητα αναφοράς κόμης</t>
+          <t>Πυκνότητα φυτών</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>crop.reference_density_plants_per_m2</t>
+          <t>crop.density_plants_per_m2</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Πυκνότητα στην οποία η κόμη θεωρείται πλήρως κλειστή (LAI = lai_max)</t>
+          <t>Φυτά ανά m² — τυπική εμπορική πυκνότητα single-stem high-wire καλλιέργειας</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1387,61 +1387,61 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>twin/params.py</t>
+          <t>config/greenhouse_example.yaml</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Μέγιστο LAI</t>
+          <t>Πυκνότητα αναφοράς κόμης</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>crop.lai_max</t>
+          <t>crop.reference_density_plants_per_m2</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>2.5 φ/m²</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Μέγιστος δείκτης φυλλικής επιφάνειας (Leaf Area Index)</t>
+          <t>Πυκνότητα στην οποία η κόμη θεωρείται πλήρως κλειστή (LAI = lai_max)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Εύλογη τάξη μεγέθους (συνήθως αναφέρεται 3-4), δεν τεκμηριώθηκε ξεχωριστά</t>
+          <t>papers/vt-extension-spes-474.md · papers/peet-welles-greenhouse-tomato-production.md</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>config/greenhouse_example.yaml</t>
+          <t>twin/params.py</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Μέρες ράμπας LAI</t>
+          <t>Μέγιστο LAI</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>crop.lai_ramp_days</t>
+          <t>crop.lai_max</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Μέρες μετά τη φύτευση μέχρι να φτάσει περίπου στο μέγιστο LAI</t>
+          <t>Μέγιστος δείκτης φυλλικής επιφάνειας (Leaf Area Index)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Μηχανολογική εκτίμηση, δεν τεκμηριώθηκε</t>
+          <t>Εύλογη τάξη μεγέθους (συνήθως αναφέρεται 3-4), δεν τεκμηριώθηκε ξεχωριστά</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Έναρξη καρποφορίας</t>
+          <t>Μέρες ράμπας LAI</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>crop.fruiting_start_days</t>
+          <t>crop.lai_ramp_days</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Μέρες μετά τη φύτευση πριν ξεκινήσει ο διαμερισμός προς τον καρπό</t>
+          <t>Μέρες μετά τη φύτευση μέχρι να φτάσει περίπου στο μέγιστο LAI</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Εύλογη τάξη μεγέθους, δεν τεκμηριώθηκε</t>
+          <t>Μηχανολογική εκτίμηση, δεν τεκμηριώθηκε</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1505,17 +1505,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Ράμπα καρποφορίας</t>
+          <t>Έναρξη καρποφορίας</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>crop.fruiting_ramp_days</t>
+          <t>crop.fruiting_start_days</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Μέρες μέχρι να φτάσει το πλήρες ποσοστό διαμερισμού προς τον καρπό</t>
+          <t>Μέρες μετά τη φύτευση πριν ξεκινήσει ο διαμερισμός προς τον καρπό</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Δεν τεκμηριώθηκε</t>
+          <t>Εύλογη τάξη μεγέθους, δεν τεκμηριώθηκε</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1542,54 +1542,54 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Μέγιστο ποσοστό διαμερισμού καρπού</t>
+          <t>Ράμπα καρποφορίας</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>crop.fruit_partition_fraction_max</t>
+          <t>crop.fruiting_ramp_days</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Μέγιστο ποσοστό ξηράς ουσίας που κατευθύνεται στον καρπό στην αιχμή καρποφορίας. Ανέβηκε από 0.6 → 0.85 στις 2026-08-19.</t>
+          <t>Μέρες μέχρι να φτάσει το πλήρες ποσοστό διαμερισμού προς τον καρπό</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>papers/bertin-gary-1993-tomgro.md — TOMGRO, Bertin &amp; Gary 1993 (80-90%)</t>
+          <t>Δεν τεκμηριώθηκε</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>config/greenhouse_example.yaml, twin/params.py</t>
+          <t>config/greenhouse_example.yaml</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Ξηρά ουσία καρπού</t>
+          <t>Μέγιστο ποσοστό διαμερισμού καρπού</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>crop.dry_matter_content_fruit</t>
+          <t>crop.fruit_partition_fraction_max</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1599,34 +1599,34 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Ποσοστό ξηράς ουσίας νωπού καρπού τομάτας (5.5%)</t>
+          <t>Μέγιστο ποσοστό ξηράς ουσίας που κατευθύνεται στον καρπό στην αιχμή καρποφορίας. Ανέβηκε από 0.6 → 0.85 στις 2026-08-19.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>papers/usda-fdc-tomato-170457.md — USDA FoodData Central</t>
+          <t>papers/bertin-gary-1993-tomgro.md — TOMGRO, Bertin &amp; Gary 1993 (80-90%)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>config/greenhouse_example.yaml</t>
+          <t>config/greenhouse_example.yaml, twin/params.py</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Μέγιστος ρυθμός φωτοσύνθεσης</t>
+          <t>Ξηρά ουσία καρπού</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>P_MAX_UMOL_M2_LEAF_S</t>
+          <t>crop.dry_matter_content_fruit</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>20.0 µmol/m²/s</t>
+          <t>0.055</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1636,49 +1636,49 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Ρυθμός φωτοσύνθεσης σε κορεσμό φωτός/CO2/θερμοκρασίας, ανά m² φύλλου</t>
+          <t>Ποσοστό ξηράς ουσίας νωπού καρπού τομάτας (5.5%)</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>papers/researchgate-258515123-photosynthesis-ec.md — συντηρητικό άκρο του εύρους 20-40</t>
+          <t>papers/usda-fdc-tomato-170457.md — USDA FoodData Central</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>twin/crop_model.py</t>
+          <t>config/greenhouse_example.yaml</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Ημικορεσμός φωτισμού</t>
+          <t>Μέγιστος ρυθμός φωτοσύνθεσης</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>LIGHT_HALF_SAT_W_M2</t>
+          <t>P_MAX_UMOL_M2_LEAF_S</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>200.0 W/m²</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>20.0 µmol/m²/s</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Επίπεδο φωτισμού στο οποίο επιτυγχάνεται το μισό του P_max</t>
+          <t>Ρυθμός φωτοσύνθεσης σε κορεσμό φωτός/CO2/θερμοκρασίας, ανά m² φύλλου</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Εύλογη τάξη μεγέθους, δεν τεκμηριώθηκε ξεχωριστά</t>
+          <t>papers/researchgate-258515123-photosynthesis-ec.md — συντηρητικό άκρο του εύρους 20-40</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Ημικορεσμός CO2</t>
+          <t>Ημικορεσμός φωτισμού</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CO2_HALF_SAT_PPM</t>
+          <t>LIGHT_HALF_SAT_W_M2</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>200.0 ppm</t>
+          <t>200.0 W/m²</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Συγκέντρωση CO2 (σχετικά με το ambient) στο μισό της απόκρισης</t>
+          <t>Επίπεδο φωτισμού στο οποίο επιτυγχάνεται το μισό του P_max</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Εύλογο σχήμα καμπύλης, δεν τεκμηριώθηκε ξεχωριστά</t>
+          <t>Εύλογη τάξη μεγέθους, δεν τεκμηριώθηκε ξεχωριστά</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1727,17 +1727,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Ελάχιστη θερμοκρασία φωτοσύνθεσης</t>
+          <t>Ημικορεσμός CO2</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>T_MIN_C</t>
+          <t>CO2_HALF_SAT_PPM</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>10.0 °C</t>
+          <t>200.0 ppm</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Καρδιναλική ελάχιστη θερμοκρασία για φωτοσύνθεση (κάτω από αυτήν, μηδενική)</t>
+          <t>Συγκέντρωση CO2 (σχετικά με το ambient) στο μισό της απόκρισης</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Δεν αλλάχθηκε σε αυτό το πέρασμα — βλ. docs/assumptions/crop-model.md</t>
+          <t>Εύλογο σχήμα καμπύλης, δεν τεκμηριώθηκε ξεχωριστά</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1764,32 +1764,32 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Βέλτιστη θερμοκρασία φωτοσύνθεσης</t>
+          <t>Ελάχιστη θερμοκρασία φωτοσύνθεσης</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>T_OPT_C</t>
+          <t>T_MIN_C</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>27.0 °C</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>SOURCED</t>
+          <t>10.0 °C</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Καρδιναλική βέλτιστη θερμοκρασία φωτοσύνθεσης. Ανέβηκε από 24 → 27°C στις 2026-08-19.</t>
+          <t>Καρδιναλική ελάχιστη θερμοκρασία για φωτοσύνθεση (κάτω από αυτήν, μηδενική)</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>papers/researchgate-323225604-temp-vpd-review.md · papers/frontiers-2017-00365-heat-photosynthesis.md (βέλτιστο 25-35°C)</t>
+          <t>Δεν αλλάχθηκε σε αυτό το πέρασμα — βλ. docs/assumptions/crop-model.md</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1801,32 +1801,32 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Μέγιστη θερμοκρασία φωτοσύνθεσης</t>
+          <t>Βέλτιστη θερμοκρασία φωτοσύνθεσης</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>T_MAX_C</t>
+          <t>T_OPT_C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>35.0 °C</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>27.0 °C</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Καρδιναλική μέγιστη θερμοκρασία (πάνω από αυτήν, μηδενική φωτοσύνθεση)</t>
+          <t>Καρδιναλική βέλτιστη θερμοκρασία φωτοσύνθεσης. Ανέβηκε από 24 → 27°C στις 2026-08-19.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Ταιριάζει με τη βιβλιογραφία που βρέθηκε, δεν επαληθεύτηκε ξεχωριστά</t>
+          <t>papers/researchgate-323225604-temp-vpd-review.md · papers/frontiers-2017-00365-heat-photosynthesis.md (βέλτιστο 25-35°C)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1838,17 +1838,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Ρυθμός αναπνοής συντήρησης</t>
+          <t>Μέγιστη θερμοκρασία φωτοσύνθεσης</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MAINTENANCE_RESPIRATION_FRACTION_PER_DAY</t>
+          <t>T_MAX_C</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0.015 /ημέρα</t>
+          <t>35.0 °C</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Ποσοστό της συνολικής ξηράς ουσίας που 'καίγεται' με αναπνοή ανά ημέρα, στη βέλτιστη θερμοκρασία</t>
+          <t>Καρδιναλική μέγιστη θερμοκρασία (πάνω από αυτήν, μηδενική φωτοσύνθεση)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Εύλογη τάξη μεγέθους, δεν τεκμηριώθηκε ξεχωριστά</t>
+          <t>Ταιριάζει με τη βιβλιογραφία που βρέθηκε, δεν επαληθεύτηκε ξεχωριστά</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1875,69 +1875,69 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Πηγή καιρού</t>
+          <t>Ρυθμός αναπνοής συντήρησης</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>weather.source</t>
+          <t>MAINTENANCE_RESPIRATION_FRACTION_PER_DAY</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>synthetic</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (σκόπιμο)</t>
+          <t>0.015 /ημέρα</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Συνθετική γεννήτρια καιρού (sine waves) αντί για πραγματικά ιστορικά δεδομένα</t>
+          <t>Ποσοστό της συνολικής ξηράς ουσίας που 'καίγεται' με αναπνοή ανά ημέρα, στη βέλτιστη θερμοκρασία</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>docs/assumptions/weather.md — υψηλότερης αξίας μελλοντική αναβάθμιση: αλλαγή σε 'csv'</t>
+          <t>Εύλογη τάξη μεγέθους, δεν τεκμηριώθηκε ξεχωριστά</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>config/greenhouse_example.yaml</t>
+          <t>twin/crop_model.py</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Γεωγραφικό πλάτος</t>
+          <t>Πηγή καιρού</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>weather.latitude_deg</t>
+          <t>weather.source</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>37.9°</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>SITE-SPECIFIC</t>
+          <t>synthetic</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (σκόπιμο)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Πλάτος Αθήνας· ΣΗΜΕΙΩΣΗ: δεν χρησιμοποιείται ακόμα στη συνθετική γεννήτρια καιρού</t>
+          <t>Συνθετική γεννήτρια καιρού (sine waves) αντί για πραγματικά ιστορικά δεδομένα</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Δεδομένο του χρήστη (Αθήνα ως προσωρινή τοποθεσία)</t>
+          <t>docs/assumptions/weather.md — υψηλότερης αξίας μελλοντική αναβάθμιση: αλλαγή σε 'csv'</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1949,17 +1949,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Μέση ετήσια θερμοκρασία</t>
+          <t>Γεωγραφικό πλάτος</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>weather.mean_annual_temp_c</t>
+          <t>weather.latitude_deg</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>18.0 °C</t>
+          <t>37.9°</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Ταιριάζει περίπου με το κλίμα Αττικής</t>
+          <t>Πλάτος Αθήνας· ΣΗΜΕΙΩΣΗ: δεν χρησιμοποιείται ακόμα στη συνθετική γεννήτρια καιρού</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Εύλογο, δεν επαληθεύτηκε με συγκεκριμένο μετεωρολογικό dataset</t>
+          <t>Δεδομένο του χρήστη (Αθήνα ως προσωρινή τοποθεσία)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1986,32 +1986,32 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Εποχιακό εύρος θερμοκρασίας</t>
+          <t>Μέση ετήσια θερμοκρασία</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>weather.seasonal_amplitude_c</t>
+          <t>weather.mean_annual_temp_c</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>9.0 °C</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+          <t>18.0 °C</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>SITE-SPECIFIC</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Διαφορά καλοκαιριού/χειμώνα στη συνθετική καμπύλη</t>
+          <t>Ταιριάζει περίπου με το κλίμα Αττικής</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Εύλογη τάξη μεγέθους για Μεσογειακό κλίμα, δεν επαληθεύτηκε</t>
+          <t>Εύλογο, δεν επαληθεύτηκε με συγκεκριμένο μετεωρολογικό dataset</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2023,17 +2023,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Ημερήσιο εύρος θερμοκρασίας</t>
+          <t>Εποχιακό εύρος θερμοκρασίας</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>weather.diurnal_amplitude_c</t>
+          <t>weather.seasonal_amplitude_c</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>6.0 °C</t>
+          <t>9.0 °C</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Διαφορά μέρας/νύχτας στη συνθετική καμπύλη</t>
+          <t>Διαφορά καλοκαιριού/χειμώνα στη συνθετική καμπύλη</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Δεν επαληθεύτηκε με πραγματικά δεδομένα σταθμού</t>
+          <t>Εύλογη τάξη μεγέθους για Μεσογειακό κλίμα, δεν επαληθεύτηκε</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2060,17 +2060,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Μέγιστη ηλιακή ακτινοβολία</t>
+          <t>Ημερήσιο εύρος θερμοκρασίας</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>weather.peak_solar_w_m2</t>
+          <t>weather.diurnal_amplitude_c</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>850.0 W/m²</t>
+          <t>6.0 °C</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Ακτινοβολία αιχμής μεσημεριού καλοκαιριού</t>
+          <t>Διαφορά μέρας/νύχτας στη συνθετική καμπύλη</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Εύλογο για Μεσογειακά γεωγραφικά πλάτη (τυπικά 800-1000), δεν επαληθεύτηκε ξεχωριστά</t>
+          <t>Δεν επαληθεύτηκε με πραγματικά δεδομένα σταθμού</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2097,79 +2097,116 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Θερμοχωρητικότητα αέρα</t>
+          <t>Μέγιστη ηλιακή ακτινοβολία</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>AIR_VOLUMETRIC_HEAT_CAPACITY_J_M3K</t>
+          <t>weather.peak_solar_w_m2</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>1200 J/m³K</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>ΦΥΣΙΚΗ ΣΤΑΘΕΡΑ</t>
+          <t>850.0 W/m²</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Πυκνότητα αέρα (~1.2 kg/m³) × ειδική θερμότητα (~1005 J/kgK)</t>
+          <t>Ακτινοβολία αιχμής μεσημεριού καλοκαιριού</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Φυσική σταθερά — οποιαδήποτε αναφορά φυσικής/μηχανικής</t>
+          <t>Εύλογο για Μεσογειακά γεωγραφικά πλάτη (τυπικά 800-1000), δεν επαληθεύτηκε ξεχωριστά</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>twin/climate_model.py</t>
+          <t>config/greenhouse_example.yaml</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>Θερμοχωρητικότητα αέρα</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>AIR_VOLUMETRIC_HEAT_CAPACITY_J_M3K</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>1200 J/m³K</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>ΦΥΣΙΚΗ ΣΤΑΘΕΡΑ</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Πυκνότητα αέρα (~1.2 kg/m³) × ειδική θερμότητα (~1005 J/kgK)</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Φυσική σταθερά — οποιαδήποτε αναφορά φυσικής/μηχανικής</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>twin/climate_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
           <t>Πυκνότητα CO2</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>CO2_DENSITY_KG_M3</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>1.83 kg/m³</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>ΦΥΣΙΚΗ ΣΤΑΘΕΡΑ</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Πυκνότητα αερίου CO2 στους ~20°C</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Φυσική σταθερά — καταστατική εξίσωση αερίων, MW=44g/mol</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>twin/climate_model.py</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G44"/>
+  <autoFilter ref="A1:G45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Οδηγός" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2205,8 +2205,156 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Συντελεστής εξασθένησης φωτός κόμης</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CANOPY_LIGHT_EXTINCTION_COEFF</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Beer-Lambert k — ποσοστό ηλιακής ακτινοβολίας που απορροφά η κόμη ανάλογα με το LAI</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>papers/tomato-canopy-extinction-coefficient.md</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Ποσοστό ενέργειας σε διαπνοή</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>TRANSPIRATION_ENERGY_FRACTION</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Ποσοστό απορροφημένης ακτινοβολίας που μετατρέπεται σε διαπνοή (υδρατμούς) αντί αισθητή θερμότητα</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>papers/tomato-transpiration-latent-heat-fraction.md</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Λανθάνουσα θερμότητα εξάτμισης</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>LATENT_HEAT_OF_VAPORIZATION_J_KG</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2.45e6 J/kg</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>ΦΥΣΙΚΗ ΣΤΑΘΕΡΑ</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Φυσική σταθερά νερού στους ~20°C</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Standard μετεωρολογική τιμή (π.χ. FAO-56)</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Πίεση κορεσμού υδρατμών (τύπος)</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>_saturation_vapor_pressure_kpa (Tetens)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>ΦΥΣΙΚΗ ΣΤΑΘΕΡΑ</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Τυπικός μετεωρολογικός τύπος (Tetens/Magnus) για πίεση κορεσμού υδρατμών ανά θερμοκρασία</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>FAO-56 Penman-Monteith (Allen et al. 1998), standard εξίσωση</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>twin/climate_model.py</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G45"/>
+  <autoFilter ref="A1:G49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Οδηγός" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2353,8 +2353,156 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Θερμοκρασία επιφάνειας κάλυψης (κλάσμα)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>climate_control.cover_surface_temp_fraction</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Πόσο κοντά στην εξωτερική θερμοκρασία βρίσκεται η εσωτερική επιφάνεια της κάλυψης — καθορίζει πότε συμπυκνώνεται υγρασία</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>papers/greenhouse-condensation-dewpoint-physics.md (μηχανισμός sourced, τιμή engineering estimate)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/climate_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Ρυθμός συμπύκνωσης</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>climate_control.condensation_rate_constant</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>2.0 /h</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Ρυθμός χαλάρωσης πίεσης υδρατμών προς το επίπεδο κορεσμού της κρύας επιφάνειας κάλυψης</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Engineering estimate, όχι μετρημένος συντελεστής μεταφοράς μάζας</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/climate_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Setpoint αφύγρανσης</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>climate_control.dehumidification_setpoint_pct</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Στόχος RH του (εξιδανικευμένου) ενεργητικού συστήματος αφύγρανσης (OptiClima). Εύρημα: yield ευαίσθητο σε αυτή την τιμή (85%→8.4, 65%→17.5 kg/m²) αφού το VPD πλέον επηρεάζει τη φωτοσύνθεση</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Κοινή βιομηχανική πρακτική· χωρητικότητα μη διαθέσιμη από την προσφορά</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/climate_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Καρδινάλια σημεία VPD φωτοσύνθεσης</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>VPD_MIN_KPA, VPD_OPT_KPA, VPD_MAX_KPA</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>0.2, 0.85, 2.0 kPa</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Καμπύλη απόκρισης φωτοσύνθεσης στο VPD (κλείσιμο στομάτων σε υψηλό VPD)</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>papers/tomato-vpd-optimal-range.md</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G49"/>
+  <autoFilter ref="A1:G53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Στόχος RH του (εξιδανικευμένου) ενεργητικού συστήματος αφύγρανσης (OptiClima). Εύρημα: yield ευαίσθητο σε αυτή την τιμή (85%→8.4, 65%→17.5 kg/m²) αφού το VPD πλέον επηρεάζει τη φωτοσύνθεση</t>
+          <t>Στόχος RH του ενεργητικού συστήματος αφύγρανσης (OptiClima). 70% = βιβλιογραφικό βέλτιστο επικονίασης (πάνω από 80% κολλάνε γύρεις, κάτω από 60% στεγνώνει το στίγμα). Νέο yield: 15.49 kg/m² (μέσο VPD 0.88 kPa, κοντά στο optimum)</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Κοινή βιομηχανική πρακτική· χωρητικότητα μη διαθέσιμη από την προσφορά</t>
+          <t>papers/greenhouse-tomato-optimal-rh.md</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Οδηγός" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>900.0 ppm</t>
+          <t>700 ppm (ήταν 900)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Στόχος εμπλουτισμού CO2 κατά τη διάρκεια της ημέρας</t>
+          <t>Setpoint CO2 ημέρας. Διορθώθηκε: 900ppm δεν έδινε κανένα επιπλέον yield από τα 700ppm — σπατάλη χωρητικότητας δοσομέτρησης</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>papers/researchgate-323225604-temp-vpd-review.md — βέλτιστο εύρος 700-1000ppm</t>
+          <t>papers/tomato-co2-optimum-700ppm.md</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2501,8 +2501,45 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Πλατό κορεσμού CO2 φωτοσύνθεσης</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>CO2_SATURATION_PPM</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>700 ppm</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Bug fix: η καμπύλη Michaelis-Menten δεν είχε ανώτατο όριο, το yield ανέβαινε επ' άπειρον με το CO2. Μελέτη 500/700/850/1000ppm σε ντομάτα βρήκε 700ppm βέλτιστο, καμία βελτίωση πάνω από αυτό</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>papers/tomato-co2-optimum-700ppm.md</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G53"/>
+  <autoFilter ref="A1:G54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Οδηγός" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1737,22 +1737,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>200.0 ppm</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
+          <t>375 (ήταν 200)</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>PLACEHOLDER</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Συγκέντρωση CO2 (σχετικά με το ambient) στο μισό της απόκρισης</t>
+          <t>Σχήμα καμπύλης CO2. Βιοχημικά τεκμηριωμένο (Rubisco Km, Ci/Ca-adjusted ~340-430ppm). Μόνο του δεν αρκεί (ελαστικότητα &lt;1) — χρειάζεται και το CO2→LAI κανάλι από κάτω</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Εύλογο σχήμα καμπύλης, δεν τεκμηριώθηκε ξεχωριστά</t>
+          <t>papers/co2-half-saturation-tomato.md</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2538,8 +2538,45 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Ενίσχυση LAI από CO2</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>CO2_LAI_BOOST_MAX, CO2_AMBIENT_REFERENCE_PPM</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>0.2688, 420ppm</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Το CO2 μεγαλώνει τη φυλλική επιφάνεια (LAI +26.88% στα 700ppm vs ambient), όχι μόνο τη στιγμιαία φωτοσύνθεση — συσσωρευτικό κανάλι. Μαζί με το K=375 φτάνει yield gain ~56.4% ambient→700ppm (στόχος βιβλιογραφίας 56-74%)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>papers/co2-lai-growth-boost.md</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Ποσοστό μείωσης θερμικής απώλειας όταν η κουρτίνα είναι κλειστή (τη νύχτα)</t>
+          <t>Ποσοστό μείωσης ΚΑΙ θερμικής απώλειας ΚΑΙ ηλιακού κέρδους/φωτός (ίδιο ύφασμα, ίδιο ποσοστό και για τα δύο) όταν η κουρτίνα είναι κλειστή. Ανάπτυξη πλήρως αυτόματη (νύχτα / πολλή ζέστη / κρύο με έλεγχο οφέλους έναντι χαμένου ήλιου) — όχι πλέον ρυθμιζόμενο ωράριο.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>config/greenhouse_example.yaml, twin/climate_model.py</t>
+          <t>config/greenhouse_example.yaml, twin/climate_model.py, twin/simulate.py, twin/crop_model.py (μέσω simulate.py)</t>
         </is>
       </c>
     </row>
@@ -2572,6 +2572,80 @@
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Περιθώριο ασφαλείας CHP για κουρτίνα</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>climate_control.chp_heat_margin_fraction</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Η κουρτίνα ενεργοποιείται για λόγο κρύου όταν η απαιτούμενη ισχύς θέρμανσης ξεπερνά το 90% της σταθερής ισχύος CHP (όχι το 100%, ώστε να προλάβει πριν χαθεί το setpoint) — επιλογή μηχανικής ασφάλειας από τον χρήστη, όχι βιβλιογραφική τιμή</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Επιλογή χρήστη, δεν υπάρχει βιβλιογραφική πηγή</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/climate_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Κατώφλι σκίασης (ζέστη)</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>VENT_RAMP_BAND_C (twin/climate_model.py, σταθερά κώδικα)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>5.0°C</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Η κουρτίνα κλείνει για σκίαση μόνο όταν ούτε ο πλήρης αερισμός θα αρκούσε (vent_setpoint + 5°C, όχι απλά το σημείο που ξεκινά ο αερισμός) — bug fix: με το χαμηλότερο κατώφλι η κουρτίνα σκίαζε ~59% των ημερήσιων ωρών χωρίς πραγματικό λόγο και το yield έπεφτε ~17%</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>papers/thermal-screen-automatic-control-logic.md</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>twin/climate_model.py</t>
         </is>
       </c>
     </row>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2646,6 +2646,43 @@
       <c r="G57" s="2" t="inlineStr">
         <is>
           <t>twin/climate_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Πηγή καιρού (τυπικό έτος)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>weather.source=csv_typical_year, weather.csv_path</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>10ετία 2015-2024, Αλεξάνδρεια Ημαθίας</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>SOURCED (script έτοιμο, δεν έχει τρέξει ακόμα)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Πραγματικά ιστορικά δεδομένα (θερμοκρασία/υγρασία/ηλιακή ακτινοβολία) από Open-Meteo, μέσος όρος ανά μήνα/ημέρα/ώρα σε 'τυπικό έτος' — αντικαθιστά το συνθετικό ημιτονοειδές μοντέλο καιρού. Χρειάζεται να τρέξει το scripts/fetch_weather.py από περιβάλλον με πρόσβαση internet (το sandbox δεν έχει).</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>papers/open-meteo-historical-weather-api.md</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>twin/weather.py, scripts/fetch_weather.py</t>
         </is>
       </c>
     </row>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -1927,12 +1927,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (σκόπιμο)</t>
+          <t>PLACEHOLDER (fallback, όχι πλέον default)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Συνθετική γεννήτρια καιρού (sine waves) αντί για πραγματικά ιστορικά δεδομένα</t>
+          <t>Συνθετική γεννήτρια καιρού (sine waves), κρατιέται μόνο ως fallback source — δες τη γραμμή 'Πηγή καιρού (τυπικό έτος)' για την ενεργή πηγή</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>SOURCED (script έτοιμο, δεν έχει τρέξει ακόμα)</t>
+          <t>SOURCED (ενεργό)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Πραγματικά ιστορικά δεδομένα (θερμοκρασία/υγρασία/ηλιακή ακτινοβολία) από Open-Meteo, μέσος όρος ανά μήνα/ημέρα/ώρα σε 'τυπικό έτος' — αντικαθιστά το συνθετικό ημιτονοειδές μοντέλο καιρού. Χρειάζεται να τρέξει το scripts/fetch_weather.py από περιβάλλον με πρόσβαση internet (το sandbox δεν έχει).</t>
+          <t>Πραγματικά ιστορικά δεδομένα (θερμοκρασία/υγρασία/ηλιακή ακτινοβολία) από Open-Meteo, μέσος όρος ανά μήνα/ημέρα/ώρα σε 'τυπικό έτος' — είναι πλέον η ενεργή πηγή καιρού (config/greenhouse_example.yaml). Εύρημα: η αλλαγή από συνθετικό σε πραγματικό καιρό ρίχνει την ελάχιστη εσωτερική θερμοκρασία στους ~3.9°C τις πιο κρύες νύχτες — η CHP (1150kW) δεν επαρκεί πάντα το χειμώνα σε πραγματικές συνθήκες. Yield 150 ημερών: 15.55→14.11 kg/m², κατανάλωση 391k→545k kWh.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Η κουρτίνα κλείνει για σκίαση μόνο όταν ούτε ο πλήρης αερισμός θα αρκούσε (vent_setpoint + 5°C, όχι απλά το σημείο που ξεκινά ο αερισμός) — bug fix: με το χαμηλότερο κατώφλι η κουρτίνα σκίαζε ~59% των ημερήσιων ωρών χωρίς πραγματικό λόγο και το yield έπεφτε ~17%</t>
+          <t>Η κουρτίνα κλείνει για σκίαση μόνο όταν ούτε ο πλήρης αερισμός θα αρκούσε — ελέγχεται τώρα (2026-08-25) εφαρμόζοντας πραγματικά τον υπολογισμό πλήρους αερισμού (_ventilated_temp), όχι με σταθερό περιθώριο. Bug fix: ο αερισμός υπερέβαλλε και γκρέμιζε τη θερμοκρασία μέχρι την εξωτερική αντί να σταματά στο δικό του στόχο (vent_setpoint) — γι' αυτό νωρίτερα φαινόταν λανθασμένα ότι δεν έφτανε η CHP.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Πραγματικά ιστορικά δεδομένα (θερμοκρασία/υγρασία/ηλιακή ακτινοβολία) από Open-Meteo, μέσος όρος ανά μήνα/ημέρα/ώρα σε 'τυπικό έτος' — είναι πλέον η ενεργή πηγή καιρού (config/greenhouse_example.yaml). Εύρημα: η αλλαγή από συνθετικό σε πραγματικό καιρό ρίχνει την ελάχιστη εσωτερική θερμοκρασία στους ~3.9°C τις πιο κρύες νύχτες — η CHP (1150kW) δεν επαρκεί πάντα το χειμώνα σε πραγματικές συνθήκες. Yield 150 ημερών: 15.55→14.11 kg/m², κατανάλωση 391k→545k kWh.</t>
+          <t>Πραγματικά ιστορικά δεδομένα (θερμοκρασία/υγρασία/ηλιακή ακτινοβολία) από Open-Meteo, μέσος όρος ανά μήνα/ημέρα/ώρα σε 'τυπικό έτος' — ενεργή πηγή καιρού (config/greenhouse_example.yaml). Αποκάλυψε ένα πραγματικό bug στον αερισμό (βλ. γραμμή 'Κατώφλι σκίασης') που το συνθετικό μοντέλο έκρυβε — μετά τη διόρθωση: yield 150 ημερών 14.11→32.79 kg/m², min εσωτερική θερμοκρασία 3.9°C→15.6°C.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2683,6 +2683,80 @@
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>twin/weather.py, scripts/fetch_weather.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Ενεργοποίηση fan-pad ψύξης</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>climate_control.fan_pad_cooling_enabled</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Επιλογή config</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Αρχική on/off επιλογή στο config για το αν το θερμοκήπιο διαθέτει σύστημα εξατμιστικής ψύξης fan-pad — ζητήθηκε ρητά από τον χρήστη. Off by default: η προσφορά (OptiClima cooling panels) δεν επιβεβαιώνει αν αφορά fan-pad θερμοκρασιακή ψύξη ή μόνο αφύγρανση.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Επιλογή χρήστη, δεν υπάρχει βιβλιογραφική πηγή</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/climate_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Απόδοση fan-pad ψύξης</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>climate_control.fan_pad_efficiency</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Κλάσμα απόστασης από ξηρή εξωτερική θερμοκρασία προς τον υγρό βολβό (wet-bulb) που φτάνει ο αέρας μετά τα pads — UF/IFAS 85% για καλά συντηρημένο σύστημα, Alabama Extension 70-85%. Χρησιμοποιείται μαζί με τύπο Stull (2011) για wet-bulb. Ενεργοποιεί ταυτόχρονα ψύξη ΚΑΙ αύξηση υγρασίας (αδιαβατική διεργασία) στον ενεργό αερισμό.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>papers/fan-pad-evaporative-cooling.md</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>twin/climate_model.py</t>
         </is>
       </c>
     </row>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true (ενεργό σε αυτό το config, default false)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Αρχική on/off επιλογή στο config για το αν το θερμοκήπιο διαθέτει σύστημα εξατμιστικής ψύξης fan-pad — ζητήθηκε ρητά από τον χρήστη. Off by default: η προσφορά (OptiClima cooling panels) δεν επιβεβαιώνει αν αφορά fan-pad θερμοκρασιακή ψύξη ή μόνο αφύγρανση.</t>
+          <t>Αρχική on/off επιλογή στο config για το αν το θερμοκήπιο διαθέτει σύστημα εξατμιστικής ψύξης fan-pad — ζητήθηκε ρητά από τον χρήστη. Ενεργοποιήθηκε στο ενεργό config μετά από δοκιμή 300 ημερών (1/3/2027, καλύπτει καλοκαίρι) που έδειξε μεγάλο όφελος: max εσωτερική θερμοκρασία 35.6°C→25.5°C, ώρες &gt;28°C 955→0, yield 76.67→92.26 kg/m². Default false στον κώδικα για νέα configs, καθώς δεν έχει επιβεβαιωθεί αν η πραγματική προσφορά (OptiClima cooling panels) αφορά fan-pad θερμοκρασιακή ψύξη ή μόνο αφύγρανση.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2757,6 +2757,43 @@
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>twin/climate_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Φωτοσύνθεση κόμης (self-shading)</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>_canopy_light_response (twin/crop_model.py)</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>k=0.75 (ίδιο με το υπάρχον)</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>SOURCED, bug fix</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Πριν: gross assimilation = ρυθμός ενός φύλλου στο πλήρες φως × LAI — σαν όλα τα φύλλα να έβλεπαν τον ίδιο ήλιο. Πραγματικά τα κατώτερα φύλλα σκιάζονται. Αυτό υπερεκτιμούσε δυσανάλογα περισσότερο το χαμηλό φως (χειμώνας) παρά το υψηλό (καλοκαίρι) — Νοέμβριος (89 W/m²) έδινε σχεδόν όσο ο Μάιος (262 W/m², 3x φως). Διορθώθηκε με ολοκλήρωμα Beer-Lambert/Michaelis-Menten (de Wit/Goudriaan τύπος). Yield 300 ημερών: 92.98→42.58 kg/m² (πιο ρεαλιστικό — κάτω από ολλανδικό όριο χωρίς τεχνητό φωτισμό, ενώ πριν ήταν στο επίπεδο ρεκόρ Ολλανδίας χωρίς καν να έχουμε τεχνητό φωτισμό).</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>papers/canopy-self-shading-photosynthesis.md</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>twin/crop_model.py</t>
         </is>
       </c>
     </row>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2792,6 +2792,43 @@
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Χρέος αναπνοής (respiration deficit)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>CropState.respiration_deficit_g_m2 (twin/crop_model.py)</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER, bug fix</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Πριν: η νυχτερινή αναπνοή μείωνε τη standing biomass χωρίς καμία άλλη συνέπεια -- επειδή το LAI δεν εξαρτάται από τη standing biomass, αυτό ήταν καθαρό κέρδος (λιγότερη μελλοντική αναπνοή). Αποτέλεσμα: ζεστότερο βραδινό setpoint ανέβαζε το yield (λάθος -- η βιβλιογραφία λέει το αντίθετο, γι' αυτό το heating_setpoint_night_c=17°C). Διορθώθηκε: κάθε αρνητική ωριαία απόδοση συσσωρεύεται σε χρέος που πρέπει να αποπληρωθεί πλήρως από μελλοντική θετική ανάπτυξη πριν πάει οτιδήποτε σε καρπό. Yield 150 ημερών: 13.38→6.47 kg/m². Η αυστηρότητα (πλήρης αποπληρωμή πριν από καρπό) είναι μηχανική επιλογή, όχι βαθμονομημένη τιμή.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>docs/assumptions/crop-model.md</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>twin/crop_model.py</t>
         </is>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2829,6 +2829,43 @@
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Ευαισθησία γονιμοποίησης στη θερμοκρασία</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>FRUIT_SET_T_MIN_C, FRUIT_SET_T_OPT_C, FRUIT_SET_T_MAX_C, _fruit_set_temp_response (twin/crop_model.py)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>12.0 / 18.0 / 24.0 °C</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>SOURCED, bug fix</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Ο χρήστης βρήκε ότι ακόμα και μετά τη διόρθωση του respiration deficit, το yield συνέχιζε να ανεβαίνει απεριόριστα όσο πιο κρύα η νύχτα (μέχρι 5°C) -- έλειπε εντελώς ποινή για chilling stress. Η φωτοσύνθεση (T_MIN=10,T_OPT=27,T_MAX=35) αντέχει ευρύ εύρος θερμοκρασιών, αλλά η γονιμοποίηση (βιωσιμότητα γύρης, ανάπτυξη γυρεοσωλήνα) είναι πολύ πιο ευαίσθητη: &lt;55°F ανθόπτωση, ιδανικό 60-70°F, &gt;75°F παρεμβολή στον γυρεοσωλήνα. Νέα στενότερη καμπύλη πολλαπλασιάζει το fruit_fraction. Χρειάστηκε επίσης exponential moving average της θερμοκρασίας (12ωρο half-life) ώστε μια κρύα νύχτα να «κουβαλάει» ποινή στην επόμενη μέρα (τη νύχτα δεν υπάρχει ποτέ θετική καθαρή ανάπτυξη ώστε να τιμωρηθεί απευθείας). Αποτέλεσμα: τώρα υπάρχει πραγματική κορυφή (12°C στο τρέξιμο), όχι πια μονότονη καμπύλη -- αλλά δεν πέφτει ακριβώς στο βιβλιογραφικό 17-18°C, γνωστό open gap (βλ. crop-model.md).</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>papers/tomato-fruit-set-temperature-sensitivity.md</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>twin/crop_model.py</t>
         </is>

--- a/docs/assumptions/sources.xlsx
+++ b/docs/assumptions/sources.xlsx
@@ -2800,12 +2800,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Χρέος αναπνοής (respiration deficit)</t>
+          <t>Αναφορά αναπνοής (high-water mark)</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CropState.respiration_deficit_g_m2 (twin/crop_model.py)</t>
+          <t>CropState.respiration_reference_g_m2 (twin/crop_model.py)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Πριν: η νυχτερινή αναπνοή μείωνε τη standing biomass χωρίς καμία άλλη συνέπεια -- επειδή το LAI δεν εξαρτάται από τη standing biomass, αυτό ήταν καθαρό κέρδος (λιγότερη μελλοντική αναπνοή). Αποτέλεσμα: ζεστότερο βραδινό setpoint ανέβαζε το yield (λάθος -- η βιβλιογραφία λέει το αντίθετο, γι' αυτό το heating_setpoint_night_c=17°C). Διορθώθηκε: κάθε αρνητική ωριαία απόδοση συσσωρεύεται σε χρέος που πρέπει να αποπληρωθεί πλήρως από μελλοντική θετική ανάπτυξη πριν πάει οτιδήποτε σε καρπό. Yield 150 ημερών: 13.38→6.47 kg/m². Η αυστηρότητα (πλήρης αποπληρωμή πριν από καρπό) είναι μηχανική επιλογή, όχι βαθμονομημένη τιμή.</t>
+          <t>ΑΝΑΘΕΩΡΗΘΗΚΕ αυθημερόν: η πρώτη προσπάθεια (respiration_deficit_g_m2, "αποπλήρωσε πλήρως πριν καρπό") διόρθωσε το πρόσημο αλλά διπλομέτραγε την απώλεια -- ~480 απο ~1505 g/m2 συνολικής φωτοσύνθεσης (32%) εκτρεπόταν ΔΕΥΤΕΡΗ φορά, ενώ ήδη είχε αφαιρεθεί μία φορά από τη standing biomass. yield 150 ημερών έπεσε στα 6.21. Διορθώθηκε σωστά με respiration_reference_g_m2: τρέχον ιστορικό μέγιστο (high-water mark) της standing biomass -- η αναπνοή χρεώνεται σε αυτό, οχι στην τρέχουσα (συρρικνούμενη) τιμή, άρα μια κακή νύχτα κοστίζει ΜΙΑ φορά, όχι δύο. Αποτέλεσμα: yield 150 ημερών επέστρεψε στα 13.06 kg/m2 (κοντά στο 13.38 πριν τα δύο αυτά fixes), και το sweep νυχτερινού setpoint δείχνει σωστή κορυφή στους 16-17°C.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Ο χρήστης βρήκε ότι ακόμα και μετά τη διόρθωση του respiration deficit, το yield συνέχιζε να ανεβαίνει απεριόριστα όσο πιο κρύα η νύχτα (μέχρι 5°C) -- έλειπε εντελώς ποινή για chilling stress. Η φωτοσύνθεση (T_MIN=10,T_OPT=27,T_MAX=35) αντέχει ευρύ εύρος θερμοκρασιών, αλλά η γονιμοποίηση (βιωσιμότητα γύρης, ανάπτυξη γυρεοσωλήνα) είναι πολύ πιο ευαίσθητη: &lt;55°F ανθόπτωση, ιδανικό 60-70°F, &gt;75°F παρεμβολή στον γυρεοσωλήνα. Νέα στενότερη καμπύλη πολλαπλασιάζει το fruit_fraction. Χρειάστηκε επίσης exponential moving average της θερμοκρασίας (12ωρο half-life) ώστε μια κρύα νύχτα να «κουβαλάει» ποινή στην επόμενη μέρα (τη νύχτα δεν υπάρχει ποτέ θετική καθαρή ανάπτυξη ώστε να τιμωρηθεί απευθείας). Αποτέλεσμα: τώρα υπάρχει πραγματική κορυφή (12°C στο τρέξιμο), όχι πια μονότονη καμπύλη -- αλλά δεν πέφτει ακριβώς στο βιβλιογραφικό 17-18°C, γνωστό open gap (βλ. crop-model.md).</t>
+          <t>Πραγματική βιβλιογραφία για ευαισθησία γονιμοποίησης (κάτω από 55°F ανθόπτωση, ιδανικό 60-70°F, πάνω από 75°F παρεμβολή γυρεοσωλήνα). Χρειάστηκε EMA θερμοκρασίας (12ωρο half-life) ώστε μια κρύα νύχτα να κουβαλάει ποινή στην επόμενη μέρα. Μετά τη διόρθωση του διπλομετρήματος αναπνοής (βλ. row 62), η κορυφή του sweep πλέον πέφτει στους 16-17°C -- πολύ κοντά στο βιβλιογραφικό 17-18°C, όχι πια στους 12°C.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
